--- a/output/pdf_financials_xlsx/ROBO.xlsx
+++ b/output/pdf_financials_xlsx/ROBO.xlsx
@@ -1936,13 +1936,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.08326</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.08326</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.08326</v>
       </c>
     </row>
     <row r="93">
@@ -3332,7 +3332,11 @@
           <t>Reserves 6 2,083,260</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3879,7 +3883,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>2.08326</v>
       </c>

--- a/output/pdf_financials_xlsx/ROBO.xlsx
+++ b/output/pdf_financials_xlsx/ROBO.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006869</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004919</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.011108</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.078961</v>
+        <v>-1.08583</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.073296</v>
+        <v>-2.078215</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.788868</v>
+        <v>-1.799976</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.078518</v>
+        <v>-1.085387</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.073296</v>
+        <v>-2.078215</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.788868</v>
+        <v>-1.799976</v>
       </c>
     </row>
     <row r="30">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
